--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Floor.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Floor.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.247</t>
+    <t xml:space="preserve">EA 23.252</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Floor.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Floor.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.252</t>
+    <t xml:space="preserve">EA 23.260</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Floor.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Floor.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.281</t>
+    <t xml:space="preserve">EA 23.282 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Floor.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Floor.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="334">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -998,6 +998,33 @@
   </si>
   <si>
     <t xml:space="preserve">エイリアンの床</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">스테이지 바닥</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ステージの床</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136</t>
   </si>
 </sst>
 </file>
@@ -1226,7 +1253,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H134"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="0" width="16.15"/>
@@ -3490,6 +3517,91 @@
         <v>323</v>
       </c>
       <c r="E134" s="0" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="0" t="s">
+        <v>325</v>
+      </c>
+      <c r="B135" s="0" t="s">
+        <v>326</v>
+      </c>
+      <c r="C135" s="0" t="s">
+        <v>327</v>
+      </c>
+      <c r="D135" s="0" t="s">
+        <v>328</v>
+      </c>
+      <c r="E135" s="0" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="0" t="s">
+        <v>330</v>
+      </c>
+      <c r="B136" s="0" t="s">
+        <v>326</v>
+      </c>
+      <c r="C136" s="0" t="s">
+        <v>327</v>
+      </c>
+      <c r="D136" s="0" t="s">
+        <v>328</v>
+      </c>
+      <c r="E136" s="0" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="0" t="s">
+        <v>331</v>
+      </c>
+      <c r="B137" s="0" t="s">
+        <v>326</v>
+      </c>
+      <c r="C137" s="0" t="s">
+        <v>322</v>
+      </c>
+      <c r="D137" s="0" t="s">
+        <v>323</v>
+      </c>
+      <c r="E137" s="0" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="0" t="s">
+        <v>332</v>
+      </c>
+      <c r="B138" s="0" t="s">
+        <v>326</v>
+      </c>
+      <c r="C138" s="0" t="s">
+        <v>322</v>
+      </c>
+      <c r="D138" s="0" t="s">
+        <v>323</v>
+      </c>
+      <c r="E138" s="0" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="0" t="s">
+        <v>333</v>
+      </c>
+      <c r="B139" s="0" t="s">
+        <v>326</v>
+      </c>
+      <c r="C139" s="0" t="s">
+        <v>322</v>
+      </c>
+      <c r="D139" s="0" t="s">
+        <v>323</v>
+      </c>
+      <c r="E139" s="0" t="s">
         <v>324</v>
       </c>
     </row>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Floor.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Floor.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="353">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -571,6 +571,15 @@
     <t xml:space="preserve">71</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cute floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">かわいい床</t>
+  </si>
+  <si>
     <t xml:space="preserve">72</t>
   </si>
   <si>
@@ -1025,6 +1034,54 @@
   </si>
   <si>
     <t xml:space="preserve">136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">귀여운 바닥</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">민무늬 바닥</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plain floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無地の床</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">트릭키한 바닥</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tricky floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">トリッキーな床</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145</t>
   </si>
 </sst>
 </file>
@@ -1253,7 +1310,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H148"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="0" width="16.15"/>
@@ -2488,58 +2545,58 @@
         <v>181</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>9</v>
+        <v>182</v>
       </c>
       <c r="C74" s="0" t="s">
         <v>78</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>79</v>
+        <v>183</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>80</v>
+        <v>184</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B75" s="0" t="s">
         <v>9</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B76" s="0" t="s">
         <v>9</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C77" s="0" t="s">
         <v>91</v>
@@ -2553,7 +2610,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B78" s="0" t="s">
         <v>99</v>
@@ -2562,273 +2619,273 @@
         <v>100</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B79" s="0" t="s">
         <v>99</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B81" s="0" t="s">
         <v>99</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B82" s="0" t="s">
         <v>99</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B83" s="0" t="s">
         <v>99</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B84" s="0" t="s">
         <v>99</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B85" s="0" t="s">
         <v>99</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="B86" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="C86" s="0" t="s">
         <v>215</v>
       </c>
-      <c r="B86" s="0" t="s">
-        <v>200</v>
-      </c>
-      <c r="C86" s="0" t="s">
-        <v>212</v>
-      </c>
       <c r="D86" s="0" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
+        <v>219</v>
+      </c>
+      <c r="B87" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="C87" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="D87" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="B87" s="0" t="s">
-        <v>200</v>
-      </c>
-      <c r="C87" s="0" t="s">
-        <v>212</v>
-      </c>
-      <c r="D87" s="0" t="s">
-        <v>213</v>
-      </c>
       <c r="E87" s="0" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="B88" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="C88" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="D88" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="E88" s="0" t="s">
         <v>217</v>
-      </c>
-      <c r="B88" s="0" t="s">
-        <v>200</v>
-      </c>
-      <c r="C88" s="0" t="s">
-        <v>212</v>
-      </c>
-      <c r="D88" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="E88" s="0" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E92" s="0" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E93" s="0" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C94" s="0" t="s">
         <v>78</v>
@@ -2842,180 +2899,180 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B95" s="0" t="s">
         <v>99</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B96" s="0" t="s">
         <v>99</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E96" s="0" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B97" s="0" t="s">
         <v>99</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B98" s="0" t="s">
         <v>99</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E98" s="0" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B99" s="0" t="s">
         <v>99</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="B100" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="C100" s="0" t="s">
         <v>242</v>
       </c>
-      <c r="B100" s="0" t="s">
+      <c r="D100" s="0" t="s">
         <v>243</v>
       </c>
-      <c r="C100" s="0" t="s">
-        <v>239</v>
-      </c>
-      <c r="D100" s="0" t="s">
-        <v>240</v>
-      </c>
       <c r="E100" s="0" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E102" s="0" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E103" s="0" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C104" s="0" t="s">
         <v>100</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E104" s="0" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C105" s="0" t="s">
         <v>85</v>
@@ -3029,10 +3086,10 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C106" s="0" t="s">
         <v>85</v>
@@ -3046,7 +3103,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B107" s="0" t="s">
         <v>161</v>
@@ -3063,10 +3120,10 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C108" s="0" t="s">
         <v>35</v>
@@ -3080,10 +3137,10 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C109" s="0" t="s">
         <v>31</v>
@@ -3097,10 +3154,10 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C110" s="0" t="s">
         <v>78</v>
@@ -3114,10 +3171,10 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C111" s="0" t="s">
         <v>31</v>
@@ -3131,10 +3188,10 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C112" s="0" t="s">
         <v>31</v>
@@ -3148,10 +3205,10 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C113" s="0" t="s">
         <v>78</v>
@@ -3165,10 +3222,10 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="B114" s="0" t="s">
         <v>268</v>
-      </c>
-      <c r="B114" s="0" t="s">
-        <v>265</v>
       </c>
       <c r="C114" s="0" t="s">
         <v>78</v>
@@ -3182,61 +3239,61 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E115" s="0" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E116" s="0" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
+        <v>281</v>
+      </c>
+      <c r="B117" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="C117" s="0" t="s">
         <v>278</v>
       </c>
-      <c r="B117" s="0" t="s">
+      <c r="D117" s="0" t="s">
         <v>279</v>
       </c>
-      <c r="C117" s="0" t="s">
-        <v>275</v>
-      </c>
-      <c r="D117" s="0" t="s">
-        <v>276</v>
-      </c>
       <c r="E117" s="0" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C118" s="0" t="s">
         <v>61</v>
@@ -3250,10 +3307,10 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C119" s="0" t="s">
         <v>61</v>
@@ -3267,10 +3324,10 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C120" s="0" t="s">
         <v>31</v>
@@ -3284,10 +3341,10 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C121" s="0" t="s">
         <v>61</v>
@@ -3301,10 +3358,10 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C122" s="0" t="s">
         <v>61</v>
@@ -3318,10 +3375,10 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="B123" s="0" t="s">
         <v>286</v>
-      </c>
-      <c r="B123" s="0" t="s">
-        <v>283</v>
       </c>
       <c r="C123" s="0" t="s">
         <v>61</v>
@@ -3335,112 +3392,112 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E124" s="0" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E125" s="0" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="0" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E126" s="0" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="0" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E128" s="0" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="0" t="s">
+        <v>313</v>
+      </c>
+      <c r="B129" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="C129" s="0" t="s">
         <v>310</v>
       </c>
-      <c r="B129" s="0" t="s">
-        <v>306</v>
-      </c>
-      <c r="C129" s="0" t="s">
-        <v>307</v>
-      </c>
       <c r="D129" s="0" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E129" s="0" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C130" s="0" t="s">
         <v>31</v>
@@ -3454,10 +3511,10 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C131" s="0" t="s">
         <v>31</v>
@@ -3471,10 +3528,10 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C132" s="0" t="s">
         <v>31</v>
@@ -3488,121 +3545,274 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E133" s="0" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D134" s="0" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E134" s="0" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D135" s="0" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E135" s="0" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="0" t="s">
+        <v>333</v>
+      </c>
+      <c r="B136" s="0" t="s">
+        <v>329</v>
+      </c>
+      <c r="C136" s="0" t="s">
         <v>330</v>
       </c>
-      <c r="B136" s="0" t="s">
-        <v>326</v>
-      </c>
-      <c r="C136" s="0" t="s">
-        <v>327</v>
-      </c>
       <c r="D136" s="0" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E136" s="0" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="0" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B137" s="0" t="s">
+        <v>329</v>
+      </c>
+      <c r="C137" s="0" t="s">
+        <v>325</v>
+      </c>
+      <c r="D137" s="0" t="s">
         <v>326</v>
       </c>
-      <c r="C137" s="0" t="s">
-        <v>322</v>
-      </c>
-      <c r="D137" s="0" t="s">
-        <v>323</v>
-      </c>
       <c r="E137" s="0" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B138" s="0" t="s">
+        <v>329</v>
+      </c>
+      <c r="C138" s="0" t="s">
+        <v>325</v>
+      </c>
+      <c r="D138" s="0" t="s">
         <v>326</v>
       </c>
-      <c r="C138" s="0" t="s">
-        <v>322</v>
-      </c>
-      <c r="D138" s="0" t="s">
-        <v>323</v>
-      </c>
       <c r="E138" s="0" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B139" s="0" t="s">
+        <v>329</v>
+      </c>
+      <c r="C139" s="0" t="s">
+        <v>325</v>
+      </c>
+      <c r="D139" s="0" t="s">
         <v>326</v>
       </c>
-      <c r="C139" s="0" t="s">
-        <v>322</v>
-      </c>
-      <c r="D139" s="0" t="s">
-        <v>323</v>
-      </c>
       <c r="E139" s="0" t="s">
-        <v>324</v>
+        <v>327</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="0" t="s">
+        <v>337</v>
+      </c>
+      <c r="B140" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="C140" s="0" t="s">
+        <v>338</v>
+      </c>
+      <c r="D140" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="E140" s="0" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="0" t="s">
+        <v>339</v>
+      </c>
+      <c r="B141" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="C141" s="0" t="s">
+        <v>340</v>
+      </c>
+      <c r="D141" s="0" t="s">
+        <v>341</v>
+      </c>
+      <c r="E141" s="0" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="0" t="s">
+        <v>343</v>
+      </c>
+      <c r="B142" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="C142" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="D142" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="E142" s="0" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="0" t="s">
+        <v>344</v>
+      </c>
+      <c r="B143" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="C143" s="0" t="s">
+        <v>345</v>
+      </c>
+      <c r="D143" s="0" t="s">
+        <v>346</v>
+      </c>
+      <c r="E143" s="0" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="0" t="s">
+        <v>348</v>
+      </c>
+      <c r="B144" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="C144" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="D144" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="E144" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="0" t="s">
+        <v>349</v>
+      </c>
+      <c r="B145" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="C145" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="D145" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E145" s="0" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="0" t="s">
+        <v>350</v>
+      </c>
+      <c r="B146" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="C146" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="D146" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E146" s="0" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="0" t="s">
+        <v>351</v>
+      </c>
+      <c r="B147" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="C147" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D147" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E147" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="0" t="s">
+        <v>352</v>
+      </c>
+      <c r="B148" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="C148" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="D148" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="E148" s="0" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
